--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Anagrafe.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Anagrafe.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="124">
   <si>
     <r>
       <t xml:space="preserve">
@@ -750,8 +750,9 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve">
-Puoi pagare direttamente in app premendo “Vedi Avviso”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
-Per maggiori informazioni o per richiedere assistenza, contattaci tramite i canali che trovi nella scheda servizio o [visita questo sito](URL).
+Puoi pagare direttamente in app premendo “Paga”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
+Se hai già provveduto a pagare l'avviso, ignora questo messaggio.
+Per maggiori informazioni o per richiedere assistenza, contattaci tramite i canali che trovi nella scheda servizio.
 In fase di pagamento, se previsto dall'ente, l'importo riportato nel messaggio potrebbe subire variazioni.</t>
     </r>
   </si>
@@ -841,7 +842,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> altri documenti. 
+      <t xml:space="preserve"> altri documenti.
 Consulta il riepilogo della richiesta,[visita questo sito](URL).</t>
     </r>
   </si>
@@ -1162,7 +1163,7 @@
     <t>Disdici appuntamento</t>
   </si>
   <si>
-    <t>Vedi Avviso</t>
+    <t>Paga (inserito automaticamente dall'app se il messaggio prevede un avviso di pagamento pagoPA)</t>
   </si>
   <si>
     <t>Aggiungi documenti</t>
@@ -1188,7 +1189,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
@@ -1283,17 +1284,6 @@
       </rPr>
       <t>Note aggiuntive</t>
     </r>
-  </si>
-  <si>
-    <t>✨Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi dell'appuntamento tramite notifica push.</t>
-  </si>
-  <si>
-    <t>✨ Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi della scadenza tramite notifica push.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promemoria automatici — Messaggi Premium
-Impostando il messaggio di Avviso di pagamento come Messaggio Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, non è necessario inviare il seguente messaggio di promemoria.
-Gli utenti che hanno dato il loro consenso, infatti, riceveranno automaticamente una notifica push sui loro dispositivi all’avvicinarsi della scadenza.</t>
   </si>
   <si>
     <t>L'invio di questo messaggio serve a comunicare al cittadino i passi successivi alla chiusura della pratica. Se la chiusura della pratica non implica alcuna azione successiva, consigliamo di non inviare questo messaggio.</t>
@@ -2223,13 +2213,13 @@
         <v>60</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>123</v>
+        <v>60</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>124</v>
+        <v>60</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>125</v>
+        <v>60</v>
       </c>
       <c r="F11" s="34" t="s">
         <v>60</v>
@@ -2241,7 +2231,7 @@
         <v>60</v>
       </c>
       <c r="I11" s="34" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="J11" s="34" t="s">
         <v>60</v>
